--- a/GCC_Landscape_Oct26.xlsx
+++ b/GCC_Landscape_Oct26.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -606,6 +606,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="92" customWidth="1" min="10" max="10"/>
     <col width="58" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -651,6 +652,7 @@
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="6" t="n"/>
@@ -686,6 +688,11 @@
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Source links</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>Team input vs. review (per bucket)</t>
         </is>
       </c>
     </row>
@@ -704,7 +711,8 @@
       <c r="H4" s="10" t="n"/>
       <c r="I4" s="10" t="n"/>
       <c r="J4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="11" t="n"/>
     </row>
     <row r="5" ht="119.85" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -891,6 +899,77 @@
           </r>
         </is>
       </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="6" ht="109.5" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -1051,8 +1130,79 @@
           </r>
         </is>
       </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="29" customHeight="1">
+    <row r="7" ht="54.3" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <r>
@@ -1138,6 +1288,77 @@
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr"/>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="8" ht="109.5" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -1299,6 +1520,77 @@
           </r>
         </is>
       </c>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -1460,6 +1752,77 @@
           </r>
         </is>
       </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="10" ht="140.55" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -1656,6 +2019,77 @@
           </r>
         </is>
       </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="11" ht="119.85" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -1806,6 +2240,77 @@
           </r>
         </is>
       </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="12" ht="98" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
@@ -2001,6 +2506,77 @@
           </r>
         </is>
       </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="13" ht="119.85" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -2196,6 +2772,77 @@
           </r>
         </is>
       </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="14" ht="68.09999999999999" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
@@ -2312,6 +2959,77 @@
           </r>
         </is>
       </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="15" ht="119.85" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -2464,6 +3182,77 @@
           </r>
         </is>
       </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="16" ht="109.5" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -2615,6 +3404,77 @@
           </r>
         </is>
       </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="17" ht="98" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
@@ -2810,6 +3670,77 @@
           </r>
         </is>
       </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (no credible source, wrong bucket), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (no credible source, incorrect)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="18" ht="99.14999999999999" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -2971,6 +3902,77 @@
           </r>
         </is>
       </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="19" ht="57.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -3096,6 +4098,77 @@
           </r>
         </is>
       </c>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 3, added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="20" ht="75" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -3255,6 +4328,77 @@
           </r>
         </is>
       </c>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 2 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="21" ht="109.5" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -3450,6 +4594,77 @@
           </r>
         </is>
       </c>
+      <c r="L21" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (outdated), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (wrong bucket), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 outdated), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="22" ht="99.14999999999999" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -3635,8 +4850,79 @@
           </r>
         </is>
       </c>
+      <c r="L22" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 no credible source), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="23" ht="52" customHeight="1">
+    <row r="23" ht="54.3" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <r>
@@ -3756,6 +5042,77 @@
             </rPr>
             <t xml:space="preserve">
 https://www.swissre.com/profile/Amit_Kalra/ip_f2cb75</t>
+          </r>
+        </is>
+      </c>
+      <c r="L23" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (outdated), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
           </r>
         </is>
       </c>
@@ -3920,6 +5277,77 @@
           </r>
         </is>
       </c>
+      <c r="L24" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="25" ht="130.2" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -4149,6 +5577,77 @@
           </r>
         </is>
       </c>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="26" ht="130.2" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -4345,6 +5844,77 @@
           </r>
         </is>
       </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source), added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (no credible source, wrong bucket), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="27" ht="109.5" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -4506,6 +6076,77 @@
           </r>
         </is>
       </c>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (no credible source, wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="28" ht="171.6" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -4737,6 +6378,77 @@
           </r>
         </is>
       </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 wrong bucket), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="29" ht="161.25" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -4934,6 +6646,77 @@
           </r>
         </is>
       </c>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source), added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 no credible source), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 wrong bucket), added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="30" ht="99.14999999999999" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -5095,6 +6878,77 @@
           </r>
         </is>
       </c>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 no credible source), added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="31" ht="150.9" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -5291,6 +7145,77 @@
           </r>
         </is>
       </c>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 3, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (wrong bucket)</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="32" ht="86.5" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
@@ -5486,6 +7411,77 @@
           </r>
         </is>
       </c>
+      <c r="L32" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="33" ht="78.45" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -5646,6 +7642,77 @@
           </r>
         </is>
       </c>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="34" ht="57.75" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -5771,6 +7838,77 @@
           </r>
         </is>
       </c>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → dropped 3 (2 wrong bucket, no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="35" ht="57.75" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
@@ -5896,6 +8034,77 @@
           </r>
         </is>
       </c>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (incorrect), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → dropped 3 (3 incorrect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="36" ht="99.14999999999999" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
@@ -6056,6 +8265,77 @@
           </r>
         </is>
       </c>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="37" ht="78.45" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
@@ -6216,6 +8496,77 @@
           </r>
         </is>
       </c>
+      <c r="L37" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → dropped 3 (2 no credible source, wrong bucket), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="38" ht="98" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
@@ -6411,8 +8762,79 @@
           </r>
         </is>
       </c>
+      <c r="L38" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1, added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (incorrect, wrong bucket), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="39" ht="52" customHeight="1">
+    <row r="39" ht="54.3" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <r>
@@ -6533,6 +8955,77 @@
             <t xml:space="preserve">
 https://www.uniindia.com/business-economy/business-haryana-pfi-innovation-centre/188639
 https://jobs.weekday.works/wkdyw7sa88</t>
+          </r>
+        </is>
+      </c>
+      <c r="L39" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 no credible source), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (incorrect, no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
           </r>
         </is>
       </c>
@@ -6732,6 +9225,77 @@
           </r>
         </is>
       </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (no credible source, incorrect), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (wrong bucket, no credible source), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="41" ht="57.75" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
@@ -6857,8 +9421,79 @@
           </r>
         </is>
       </c>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 wrong bucket), added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (incorrect, wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 5 items → dropped 5 (2 no credible source, 3 wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="42" ht="52" customHeight="1">
+    <row r="42" ht="54.3" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
           <r>
@@ -6978,6 +9613,77 @@
             </rPr>
             <t xml:space="preserve">
 https://builtin.com/job/finance-lead/3082704</t>
+          </r>
+        </is>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
           </r>
         </is>
       </c>
@@ -7167,6 +9873,77 @@
           </r>
         </is>
       </c>
+      <c r="L43" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 1, dropped 2 (2 no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect), added 2 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="44" ht="75" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
@@ -7324,6 +10101,77 @@
             <t xml:space="preserve">
 https://jobs.weekday.works/walk-ins-at-fnfi-full-search-current-owner-two-owner-searchers-at-fnf-india-private-limited-wkdye0djwi
 https://www.greatplacetowork.in/great/company/fnf-india-private-limited</t>
+          </r>
+        </is>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 no credible source), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (incorrect)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (incorrect, no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
           </r>
         </is>
       </c>
@@ -7343,7 +10191,8 @@
       <c r="H45" s="10" t="n"/>
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
-      <c r="K45" s="11" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="11" t="n"/>
     </row>
     <row r="46" ht="57.75" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
@@ -7469,6 +10318,77 @@
           </r>
         </is>
       </c>
+      <c r="L46" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="47" ht="98" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
@@ -7664,6 +10584,77 @@
           </r>
         </is>
       </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="48" ht="57.75" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
@@ -7789,8 +10780,79 @@
           </r>
         </is>
       </c>
+      <c r="L48" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="49" ht="52" customHeight="1">
+    <row r="49" ht="54.3" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
           <r>
@@ -7911,6 +10973,77 @@
             <t xml:space="preserve">
 https://www.lloyds.com/insights/news/new-local-partner-in-India
 https://www.insurancebusinessmag.com/asia/news/breaking-news/lloyds-follows-partnerre-into-india-reinsurance-hub-570097.aspx</t>
+          </r>
+        </is>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -8039,8 +11172,79 @@
           </r>
         </is>
       </c>
+      <c r="L50" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="51" ht="52" customHeight="1">
+    <row r="51" ht="54.3" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
           <r>
@@ -8161,6 +11365,77 @@
             <t xml:space="preserve">
 https://www.rgare.com/global-presence/asia-pacific/india
 https://www.rgare.com/our-company/people/detail/sunil-sharma</t>
+          </r>
+        </is>
+      </c>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (no credible source)</t>
           </r>
         </is>
       </c>
@@ -8324,6 +11599,77 @@
           </r>
         </is>
       </c>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (no credible source)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 2, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → kept 1</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="53" ht="109.5" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
@@ -8519,8 +11865,79 @@
           </r>
         </is>
       </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 4 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="54" ht="29" customHeight="1">
+    <row r="54" ht="54.3" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
           <r>
@@ -8606,8 +12023,79 @@
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr"/>
+      <c r="L54" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (outdated)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 outdated), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="55" ht="52" customHeight="1">
+    <row r="55" ht="54.3" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
           <r>
@@ -8728,6 +12216,77 @@
             <t xml:space="preserve">
 https://axaxl.com/press-releases/axa-xl-strengthens-team-in-india-with-key-appointments
 https://axaxl.com/reinsurance/our-companies/xl-insurance-company-se</t>
+          </r>
+        </is>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (no credible source, wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 2, dropped 1 (no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -8926,6 +12485,77 @@
           </r>
         </is>
       </c>
+      <c r="L56" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → kept 1, dropped 1 (wrong bucket), added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 incorrect), added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 2, dropped 1 (no credible source), added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → added 1 new</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="57" ht="68.09999999999999" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -9051,6 +12681,77 @@
           </r>
         </is>
       </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 5 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="58" ht="99.14999999999999" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
@@ -9200,6 +12901,77 @@
             <t xml:space="preserve">
 https://asiainsurancepost.com/archives/81504
 https://insurance-edge.net/2026/06/23/bms-opens-global-capability-centre-in-mumbai/</t>
+          </r>
+        </is>
+      </c>
+      <c r="L58" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -9219,7 +12991,8 @@
       <c r="H59" s="10" t="n"/>
       <c r="I59" s="10" t="n"/>
       <c r="J59" s="10" t="n"/>
-      <c r="K59" s="11" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="11" t="n"/>
     </row>
     <row r="60" ht="57.75" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
@@ -9345,8 +13118,79 @@
           </r>
         </is>
       </c>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="61" ht="52" customHeight="1">
+    <row r="61" ht="54.3" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
         <is>
           <r>
@@ -9467,6 +13311,77 @@
             <t xml:space="preserve">
 https://eng.koreanre.co.kr/webzine/Bulletin_198/bull3.html
 https://www.reinsurancene.ws/korean-re-approved-to-establish-branch-in-indias-gift-city</t>
+          </r>
+        </is>
+      </c>
+      <c r="L61" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 3 items → kept 3, added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -9630,6 +13545,77 @@
           </r>
         </is>
       </c>
+      <c r="L62" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="63" ht="68.09999999999999" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
@@ -9755,6 +13741,77 @@
           </r>
         </is>
       </c>
+      <c r="L63" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="64" ht="99.14999999999999" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
@@ -9915,8 +13972,79 @@
           </r>
         </is>
       </c>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="65" ht="52" customHeight="1">
+    <row r="65" ht="54.3" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
         <is>
           <r>
@@ -10040,8 +14168,79 @@
           </r>
         </is>
       </c>
+      <c r="L65" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="66" ht="52" customHeight="1">
+    <row r="66" ht="54.3" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
           <r>
@@ -10162,6 +14361,77 @@
             <t xml:space="preserve">
 https://www.businesswire.com/news/home/20260608431690/en
 https://www.reinsurancene.ws/igi-to-open-a-new-branch-in-indias-gift-city-as-it-secures-license/</t>
+          </r>
+        </is>
+      </c>
+      <c r="L66" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -10290,8 +14560,79 @@
           </r>
         </is>
       </c>
+      <c r="L67" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="68" ht="47.4" customHeight="1">
+    <row r="68" ht="54.3" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
           <r>
@@ -10402,6 +14743,77 @@
             <t xml:space="preserve">
 https://echore.com/echo-re-opens-branch-office-in-gift-city-ifsc/
 https://www.reinsurancene.ws/ankur-sharma-named-principal-officer-of-echo-res-india-branch/</t>
+          </r>
+        </is>
+      </c>
+      <c r="L68" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 1 item → dropped 1 (wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FFC00000"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 2 items → dropped 2 (2 wrong bucket)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: 4 items → kept 4, added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: stated none → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -10530,6 +14942,77 @@
           </r>
         </is>
       </c>
+      <c r="L69" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="70" ht="57.75" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
@@ -10655,8 +15138,79 @@
           </r>
         </is>
       </c>
+      <c r="L70" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
-    <row r="71" ht="52" customHeight="1">
+    <row r="71" ht="54.3" customHeight="1">
       <c r="A71" s="12" t="inlineStr">
         <is>
           <r>
@@ -10777,6 +15331,77 @@
             <t xml:space="preserve">
 https://www.wam.ae/en/article/bygeu7d-adnic-open-new-branch-india
 https://meinsurancereview.com/News/ViewNewsLetterArticle/id/95245/type/MiddleEast/UAE-ADNIC-receives-licence-for-branch-in-India-s-GIFT-City</t>
+          </r>
+        </is>
+      </c>
+      <c r="L71" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
           </r>
         </is>
       </c>
@@ -10940,6 +15565,77 @@
           </r>
         </is>
       </c>
+      <c r="L72" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="73" ht="109.5" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
@@ -11101,6 +15797,77 @@
           </r>
         </is>
       </c>
+      <c r="L73" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 1 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="74" ht="68.09999999999999" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
@@ -11226,6 +15993,77 @@
           </r>
         </is>
       </c>
+      <c r="L74" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="75" ht="57.75" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
@@ -11351,6 +16189,77 @@
           </r>
         </is>
       </c>
+      <c r="L75" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 2 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="76" ht="57.75" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
@@ -11466,6 +16375,77 @@
           </r>
         </is>
       </c>
+      <c r="L76" s="19" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="77" ht="57.75" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
@@ -11591,27 +16571,98 @@
           </r>
         </is>
       </c>
+      <c r="L77" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">Technology: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Ops: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF375623"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → added 3 new</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Internal Audit: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF595959"/>
+              <sz val="8"/>
+            </rPr>
+            <t>team: blank → agreed, nothing public</t>
+          </r>
+        </is>
+      </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>Legend: a tick in Technology / Finance / Insurance Operations / Internal Audit (SOX, ICFR) means verified evidence that the function is performed or being built in India within roughly the past 1-2 years; the focus column states why each flagged bucket is flagged and the underlying trend; the source column lists the links per bucket. Group-level or parent news, registry revenue figures and bare licence events do not earn a tick. Evidence base: Oct 2026 research and audit of columns O-R (see Focus Review Log).</t>
+          <t>Legend: a tick in Technology / Finance / Insurance Operations / Internal Audit (SOX, ICFR) means verified evidence that the function is performed or being built in India within roughly the past 1-2 years; the focus column states why each flagged bucket is flagged and the underlying trend; the source column lists the links per bucket; the last column reconciles the team's original entries per bucket (kept / dropped with reason / newly added). Group-level or parent news, registry revenue figures and bare licence events do not earn a tick. Evidence base: Oct 2026 research and audit of columns O-R (see Focus Review Log).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="F2:L2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="A79:L79"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A79:K79"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/GCC_Landscape_Oct26.xlsx
+++ b/GCC_Landscape_Oct26.xlsx
@@ -2091,7 +2091,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="119.85" customHeight="1">
+    <row r="11" ht="181.95" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <r>
@@ -2140,19 +2140,19 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J11" s="15" t="inlineStr">
         <is>
           <r>
@@ -2179,6 +2179,22 @@
               <sz val="9"/>
             </rPr>
             <t>Shift to output-based model built on technology, automation and AI (Feb 2025): application development, data analytics, AI; 160k sq ft Pune expansion Oct 2024.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>Corporate-function operations including finance are a stated Centre of Excellence domain delivered from Bengaluru and Pune for 35+ AXA entities in 14 countries (Feb 2025).</t>
           </r>
           <r>
             <rPr>
@@ -2218,6 +2234,26 @@
             <t xml:space="preserve">
 https://www.business-standard.com/content/press-releases-ani/axa-global-business-services-embarks-on-a-new-era-of-transformation-as-it-celebrates-30-years-in-india-125021300860_1.html
 https://www.prnewswire.com/in/news-releases/axa-unveils-state-of-the-art-office-space-in-pune-expands-its-global-business-services-center-302271407.html</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://www.tribuneindia.com/news/business/axa-global-business-services-embarks-on-a-new-era-of-transformation-as-it-celebrates-30-years-in-india/
+https://tracxn.com/d/legal-entities/india/axa-global-business-services-private-limited/__YU7KMI_cCEU4d_R8dX_1H3gmvZ32z1HhrCxNpWhXrV0</t>
           </r>
           <r>
             <rPr>
@@ -4922,7 +4958,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="54.3" customHeight="1">
+    <row r="23" ht="75" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <r>
@@ -4971,19 +5007,19 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
           <r>
@@ -5010,6 +5046,22 @@
               <sz val="9"/>
             </rPr>
             <t>Global Business Solutions runs groupwide capability hubs in Bengaluru and Hyderabad, with Hyderabad positioned as the analytical and innovation hub for digital, data and technology (2026).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>Group Finance work runs from Bengaluru: ~70-strong Subledger Liabilities team owns L&amp;H and P&amp;C sub-ledger accounting under US GAAP, STAT and IFRS, plus finance-operations and AI/automation roles (2025-26).</t>
           </r>
           <r>
             <rPr>
@@ -5043,6 +5095,25 @@
             <t xml:space="preserve">
 https://www.swissre.com/profile/Amit_Kalra/ip_f2cb75</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://careers.swissre.com/job/Bangalore-Accountant-II-KA/1199902701</t>
+          </r>
         </is>
       </c>
       <c r="L23" s="15" t="inlineStr">
@@ -5117,7 +5188,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="109.5" customHeight="1">
+    <row r="24" ht="181.95" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <r>
@@ -5166,19 +5237,19 @@
       </c>
       <c r="G24" s="18" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
           <r>
@@ -5205,6 +5276,22 @@
               <sz val="9"/>
             </rPr>
             <t>Permanent Bengaluru GCC inaugurated Apr 2026 for AI engineering, cloud platforms, data and analytics; in-housing vendor technology work, headcount doubling to ~400 by end-2026.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>Local finance leadership being built out at the Bengaluru and Pune sites (Aug 2026), with Country Head Mohua Sengupta overseeing financial, regulatory and compliance matters since Nov 2025.</t>
           </r>
           <r>
             <rPr>
@@ -5254,6 +5341,26 @@
             <t xml:space="preserve">
 https://www.peoplematters.in/news/business/the-standard-grows-india-gcc-to-400-positioning-bengaluru-at-the-centre-of-its-innovation-strategy-51594
 https://www.thepeoplesboard.com/?p=17616</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://www.peoplematters.in/news/business/the-standard-grows-india-gcc-to-400-positioning-bengaluru-at-the-centre-of-its-innovation-strategy-51594
+https://gcc.economictimes.indiatimes.com/news/the-standard-expands-global-footprint-with-new-office-and-mohua-sengupta-as-country-head-in-india/125379556</t>
           </r>
           <r>
             <rPr>
@@ -8106,7 +8213,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="99.14999999999999" customHeight="1">
+    <row r="36" ht="119.85" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
           <r>
@@ -8155,19 +8262,19 @@
       </c>
       <c r="G36" s="18" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
           <r>
@@ -8194,6 +8301,22 @@
               <sz val="9"/>
             </rPr>
             <t>Hyderabad GCC launched Apr 2026 with 1,000+ roles across cloud engineering, data and AI, application development, cybersecurity and quality engineering; Amit Kalra heads it from Jul 2026.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>Site-level finance, procurement and vendor governance set up under new GCC COO Ganesh Rao (mid-2026), formerly Principal Financial's Head of Shared Services.</t>
           </r>
           <r>
             <rPr>
@@ -8243,6 +8366,25 @@
             <t xml:space="preserve">
 https://reinsurancene.ws/zurich-appoints-amit-kalra-to-lead-new-global-capability-center-in-india/
 https://explorer.hub71.com/news/feed/zurich-insurance-launches-global-capability-center-in-hyderabad-to-advance-ai-and-tech-capabilities</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://www.cxodigitalpulse.com/?p=61973</t>
           </r>
           <r>
             <rPr>
@@ -9688,7 +9830,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="140.55" customHeight="1">
+    <row r="43" ht="192.3" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
           <r>
@@ -9737,7 +9879,7 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
@@ -9776,6 +9918,22 @@
               <sz val="9"/>
             </rPr>
             <t>Second GCC opened in Hyderabad Jun 2026 taking India past 3,000 staff: technology, engineering, automation, analytics and GenAI application development for Health, Wealth and Investment Management.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>SOX and finance-controls team in Bengaluru (2026 hiring) supports Finance and Accounting on control documentation, testing and remediation, extending financial-reporting controls work to India.</t>
           </r>
           <r>
             <rPr>
@@ -9831,6 +9989,26 @@
             <t xml:space="preserve">
 https://gcc.economictimes.indiatimes.com/news/workplace-transformation/voya-financial-expands-presence-with-new-global-capability-center-in-hyderabad/131633042
 https://www.instahyre.com/job-332378-gen-ai-app-developer-at-voya-india-bangalore/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://accajobs.quintedge.com/jobs/sox-compliance-analyst-voya-india-7qbke6
+https://joinsaarthi.com/jobs/voya-financial/senior-associate-36367-bengaluru/5d4252df-6baa-49ac-89c2-13d092fefa5e</t>
           </r>
           <r>
             <rPr>
@@ -10194,7 +10372,7 @@
       <c r="K45" s="10" t="n"/>
       <c r="L45" s="11" t="n"/>
     </row>
-    <row r="46" ht="57.75" customHeight="1">
+    <row r="46" ht="78.45" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
           <r>
@@ -10243,19 +10421,19 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J46" s="15" t="inlineStr">
         <is>
           <r>
@@ -10266,6 +10444,22 @@
               <sz val="9"/>
             </rPr>
             <t>Facultative reinsurance underwriting branch (Mumbai)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>Local CFO Avneet Kumar Gupta sits among the Mumbai branch's key managerial persons alongside CEO and CUO, giving branch-level finance and statutory reporting capability (2025-26).</t>
           </r>
           <r>
             <rPr>
@@ -10303,7 +10497,26 @@
               <b val="1"/>
               <sz val="8"/>
             </rPr>
-            <t>Insurance Operations:</t>
+            <t>Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://axaxl.com/reinsurance/our-companies/xl-insurance-company-se</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Operations:</t>
           </r>
           <r>
             <rPr>
@@ -12095,7 +12308,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="54.3" customHeight="1">
+    <row r="55" ht="75" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
           <r>
@@ -12144,19 +12357,19 @@
       </c>
       <c r="G55" s="18" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H55" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J55" s="19" t="inlineStr">
         <is>
           <r>
@@ -12167,6 +12380,22 @@
               <sz val="9"/>
             </rPr>
             <t>Facultative reinsurance underwriting branch (Mumbai)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+Finance: </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <sz val="9"/>
+            </rPr>
+            <t>Local CFO Avneet Kumar Gupta sits among the Mumbai branch's key managerial persons alongside CEO and CUO, giving branch-level finance and statutory reporting capability (2025-26).</t>
           </r>
           <r>
             <rPr>
@@ -12204,7 +12433,26 @@
               <b val="1"/>
               <sz val="8"/>
             </rPr>
-            <t>Insurance Operations:</t>
+            <t>Finance:</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="FF0563C1"/>
+              <sz val="8"/>
+              <u val="single"/>
+            </rPr>
+            <t xml:space="preserve">
+https://axaxl.com/reinsurance/our-companies/xl-insurance-company-se</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+Insurance Operations:</t>
           </r>
           <r>
             <rPr>
@@ -13473,7 +13721,7 @@
               <rFont val="Arial"/>
               <sz val="9"/>
             </rPr>
-            <t>In-branch finance and administration lead appointed Aug 2026 (ex-GIC Re): accounting, taxation, regulatory reporting and credit control for the GIFT City branch.</t>
+            <t>In-branch finance and administration lead appointed Aug 2026 (ex-GIC Re): finance, taxation, regulatory compliance, audit management and credit control for the GIFT City branch.</t>
           </r>
           <r>
             <rPr>
@@ -13489,7 +13737,7 @@
               <rFont val="Arial"/>
               <sz val="9"/>
             </rPr>
-            <t>IFSCA branch approved Feb 2026; Head of India Chaturbhuj Bansal from Jun 2026 building a non-life treaty underwriting team, senior treaty underwriter hired Aug 2026.</t>
+            <t>IFSCA branch approved Feb 2026; Head of India Chaturbhuj Bansal (Jun 2026) building a non-life treaty underwriting and cat-modelling team, senior treaty underwriter hired Aug 2026.</t>
           </r>
           <r>
             <rPr>
@@ -14131,7 +14379,7 @@
               <rFont val="Arial"/>
               <sz val="9"/>
             </rPr>
-            <t>GIFT City branch approved Feb 2026 as PartnerRe's first India presence; CEO India Ankur Gupta from Jun 2026 serving Indian cedants with local P&amp;C underwriting.</t>
+            <t>GIFT City branch approved Feb 2026 as PartnerRe's first India presence; CEO India Ankur Gupta from Jun 2026 serving Indian cedants locally with P&amp;C reinsurance underwriting.</t>
           </r>
           <r>
             <rPr>
@@ -16643,10 +16891,10 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="40" customHeight="1">
+    <row r="79" ht="64" customHeight="1">
       <c r="A79" s="20" t="inlineStr">
         <is>
-          <t>Legend: a tick in Technology / Finance / Insurance Operations / Internal Audit (SOX, ICFR) means verified evidence that the function is performed or being built in India within roughly the past 1-2 years; the focus column states why each flagged bucket is flagged and the underlying trend; the source column lists the links per bucket; the last column reconciles the team's original entries per bucket (kept / dropped with reason / newly added). Group-level or parent news, registry revenue figures and bare licence events do not earn a tick. Evidence base: Oct 2026 research and audit of columns O-R (see Focus Review Log).</t>
+          <t>Legend: a tick means verified evidence that the function is performed or being built in India within roughly the past 1-2 years. Technology = engineering, software, AI/GenAI, data, cloud, cybersecurity, digital platforms, automation. Finance = finance and accounting incl. financial reporting (statutory/regulatory, IFRS/US GAAP), sub-ledger and technical accounting, close, FP&amp;A, treasury, tax, procurement, local CFO/finance lead. Insurance Ops = all core insurance functions: underwriting and pricing, actuarial, claims, policy administration, reinsurance (treaty/facultative, lines written, licence), product, distribution/broking support, customer service, insurance analytics. Internal Audit = SOX/ICFR testing, internal audit, controls assurance. The focus column states why each flagged bucket is flagged and the trend; the source column lists links per bucket; the last column reconciles the team's original entries per bucket (kept / dropped with reason / newly added). Group-level or parent news, registry revenue figures and bare licence events do not earn a tick. Evidence base: Oct 2026 research and audit of columns O-R (see Focus Review Log).</t>
         </is>
       </c>
     </row>

--- a/GCC_Landscape_Oct26.xlsx
+++ b/GCC_Landscape_Oct26.xlsx
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -213,10 +213,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -592,21 +592,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="92" customWidth="1" min="10" max="10"/>
-    <col width="58" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="92" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -619,78 +620,84 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Sr. (sheet)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>GCC Scale</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Offshoring Model</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Locations</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Service Portfolio and Positioning (flag = verified India activity in the past 1-2 years)</t>
         </is>
       </c>
-      <c r="G2" s="5" t="n"/>
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="n"/>
       <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="6" t="n"/>
       <c r="B3" s="6" t="n"/>
-      <c r="C3" s="7" t="n"/>
+      <c r="C3" s="6" t="n"/>
       <c r="D3" s="7" t="n"/>
       <c r="E3" s="7" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>Insurance Ops</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>Internal Audit</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Focus areas: why flagged, what the trend is</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Source links</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>Team input vs. review (per bucket)</t>
         </is>
@@ -712,11 +719,17 @@
       <c r="I4" s="10" t="n"/>
       <c r="J4" s="10" t="n"/>
       <c r="K4" s="10" t="n"/>
-      <c r="L4" s="11" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="11" t="n"/>
     </row>
     <row r="5" ht="119.85" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -736,47 +749,47 @@
           </r>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>~4,150-4,700</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Multi-line insurance &amp; asset management</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>Thiruvananthapuram, Pune, Mumbai</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J5" s="15" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -837,7 +850,7 @@
           </r>
         </is>
       </c>
-      <c r="K5" s="15" t="inlineStr">
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -899,7 +912,7 @@
           </r>
         </is>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -974,6 +987,11 @@
     <row r="6" ht="109.5" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -993,47 +1011,47 @@
           </r>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>8,000+ (company)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>P&amp;C insurance</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Pune</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="K6" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1088,7 +1106,7 @@
           </r>
         </is>
       </c>
-      <c r="K6" s="19" t="inlineStr">
+      <c r="L6" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1130,7 +1148,7 @@
           </r>
         </is>
       </c>
-      <c r="L6" s="19" t="inlineStr">
+      <c r="M6" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1205,6 +1223,11 @@
     <row r="7" ht="54.3" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -1224,47 +1247,47 @@
           </r>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>P&amp;C insurance</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Sold to Accenture (Jan 2021)</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="15" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1287,8 +1310,8 @@
           </r>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1363,6 +1386,11 @@
     <row r="8" ht="109.5" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -1382,47 +1410,47 @@
           </r>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Insurance broking &amp; risk advisory</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Bengaluru (expanded 2026), Noida, Gurugram</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1477,7 +1505,7 @@
           </r>
         </is>
       </c>
-      <c r="K8" s="19" t="inlineStr">
+      <c r="L8" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1520,7 +1548,7 @@
           </r>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
+      <c r="M8" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1595,6 +1623,11 @@
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -1614,47 +1647,47 @@
           </r>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>~3,000-3,100 (two units)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>UK motor insurance</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J9" s="15" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1709,7 +1742,7 @@
           </r>
         </is>
       </c>
-      <c r="K9" s="15" t="inlineStr">
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1752,7 +1785,7 @@
           </r>
         </is>
       </c>
-      <c r="L9" s="15" t="inlineStr">
+      <c r="M9" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1827,6 +1860,11 @@
     <row r="10" ht="140.55" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -1846,47 +1884,47 @@
           </r>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>~450 (Oct 2025)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Specialty insurance, reinsurance &amp; mortgage</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>Assisted build (ANSR)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Thiruvananthapuram (2025), Hyderabad (2025), Pune</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="K10" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1957,7 +1995,7 @@
           </r>
         </is>
       </c>
-      <c r="K10" s="19" t="inlineStr">
+      <c r="L10" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2019,7 +2057,7 @@
           </r>
         </is>
       </c>
-      <c r="L10" s="19" t="inlineStr">
+      <c r="M10" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2094,6 +2132,11 @@
     <row r="11" ht="181.95" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2113,47 +2156,47 @@
           </r>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>~4,000</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Multi-line insurance</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Bengaluru, Pune (2024)</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2214,7 +2257,7 @@
           </r>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
+      <c r="L11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2276,7 +2319,7 @@
           </r>
         </is>
       </c>
-      <c r="L11" s="15" t="inlineStr">
+      <c r="M11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2351,6 +2394,11 @@
     <row r="12" ht="98" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2370,47 +2418,47 @@
           </r>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Health insurance / health services</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Gurugram (2025)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="K12" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2481,7 +2529,7 @@
           </r>
         </is>
       </c>
-      <c r="K12" s="19" t="inlineStr">
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2542,7 +2590,7 @@
           </r>
         </is>
       </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="M12" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2617,6 +2665,11 @@
     <row r="13" ht="119.85" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2636,47 +2689,47 @@
           </r>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Not disclosed (1,000+ initial plan)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Health insurance / health services</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>Hyderabad (2024), Bengaluru</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2747,7 +2800,7 @@
           </r>
         </is>
       </c>
-      <c r="K13" s="15" t="inlineStr">
+      <c r="L13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2808,7 +2861,7 @@
           </r>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr">
+      <c r="M13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2883,6 +2936,11 @@
     <row r="14" ht="68.09999999999999" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -2893,47 +2951,47 @@
           </r>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>~50-60 (target ~600 by 2027)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Life insurance</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>BOT (Capgemini)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Hyderabad (2025)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J14" s="19" t="inlineStr">
+      <c r="K14" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2972,7 +3030,7 @@
           </r>
         </is>
       </c>
-      <c r="K14" s="19" t="inlineStr">
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2995,7 +3053,7 @@
           </r>
         </is>
       </c>
-      <c r="L14" s="19" t="inlineStr">
+      <c r="M14" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3070,6 +3128,11 @@
     <row r="15" ht="119.85" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -3080,47 +3143,47 @@
           </r>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Commercial property insurance &amp; risk engineering</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>Bengaluru (2025), Mumbai (2026)</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="J15" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3175,7 +3238,7 @@
           </r>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3218,7 +3281,7 @@
           </r>
         </is>
       </c>
-      <c r="L15" s="15" t="inlineStr">
+      <c r="M15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3293,6 +3356,11 @@
     <row r="16" ht="109.5" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -3312,47 +3380,47 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>~5,040 (GPTW)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Title insurance</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Hyderabad, Salem</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="J16" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="K16" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3397,7 +3465,7 @@
           </r>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr">
+      <c r="L16" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3440,7 +3508,7 @@
           </r>
         </is>
       </c>
-      <c r="L16" s="19" t="inlineStr">
+      <c r="M16" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3515,6 +3583,11 @@
     <row r="17" ht="98" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -3534,47 +3607,47 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>~11,500 (GPTW 2026); company site 10,000</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Insurance broking &amp; risk management</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Pune, Bengaluru, Mumbai, Kolhapur, Shimoga, Chandigarh, Kochi, Gurugram</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3645,7 +3718,7 @@
           </r>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3706,7 +3779,7 @@
           </r>
         </is>
       </c>
-      <c r="L17" s="15" t="inlineStr">
+      <c r="M17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3781,6 +3854,11 @@
     <row r="18" ht="99.14999999999999" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -3800,47 +3878,47 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>~30+</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="J18" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3895,7 +3973,7 @@
           </r>
         </is>
       </c>
-      <c r="K18" s="19" t="inlineStr">
+      <c r="L18" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3938,7 +4016,7 @@
           </r>
         </is>
       </c>
-      <c r="L18" s="19" t="inlineStr">
+      <c r="M18" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4013,6 +4091,11 @@
     <row r="19" ht="57.75" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -4032,47 +4115,47 @@
           </r>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>~20+ (2023)</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Specialty insurance &amp; reinsurance (Lloyd's India)</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI, Lloyd's India service company)</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4111,7 +4194,7 @@
           </r>
         </is>
       </c>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="L19" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4134,7 +4217,7 @@
           </r>
         </is>
       </c>
-      <c r="L19" s="15" t="inlineStr">
+      <c r="M19" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4209,6 +4292,11 @@
     <row r="20" ht="75" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -4228,47 +4316,47 @@
           </r>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>~11,000 (India-wide)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Insurance broking, risk &amp; consulting</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>Mumbai, Pune, Gurugram, Bengaluru, Chennai</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="K20" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4323,7 +4411,7 @@
           </r>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr">
+      <c r="L20" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4364,7 +4452,7 @@
           </r>
         </is>
       </c>
-      <c r="L20" s="19" t="inlineStr">
+      <c r="M20" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4439,6 +4527,11 @@
     <row r="21" ht="109.5" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -4458,47 +4551,47 @@
           </r>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>~1,800-2,100 (GPTW)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Life insurance &amp; retirement</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4569,7 +4662,7 @@
           </r>
         </is>
       </c>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="L21" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4630,7 +4723,7 @@
           </r>
         </is>
       </c>
-      <c r="L21" s="15" t="inlineStr">
+      <c r="M21" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4705,6 +4798,11 @@
     <row r="22" ht="99.14999999999999" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -4724,47 +4822,47 @@
           </r>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>6,500+</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Life insurance &amp; employee benefits</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>Noida (expanded 2026), Jaipur, Hyderabad, Pune</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="J22" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="K22" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4825,7 +4923,7 @@
           </r>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr">
+      <c r="L22" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4886,7 +4984,7 @@
           </r>
         </is>
       </c>
-      <c r="L22" s="19" t="inlineStr">
+      <c r="M22" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4961,6 +5059,11 @@
     <row r="23" ht="75" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -4980,47 +5083,47 @@
           </r>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>~2,500+</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Reinsurance</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>Bengaluru, Hyderabad (2022)</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr">
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5075,7 +5178,7 @@
           </r>
         </is>
       </c>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="L23" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5116,7 +5219,7 @@
           </r>
         </is>
       </c>
-      <c r="L23" s="15" t="inlineStr">
+      <c r="M23" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5191,6 +5294,11 @@
     <row r="24" ht="181.95" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -5210,47 +5318,47 @@
           </r>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>~175 (target ~400 by end-2026)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>Group benefits &amp; retirement insurance</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t>Captive via acquisition (Allstate)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>Bengaluru (2026), Pune</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5321,7 +5429,7 @@
           </r>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr">
+      <c r="L24" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5384,7 +5492,7 @@
           </r>
         </is>
       </c>
-      <c r="L24" s="19" t="inlineStr">
+      <c r="M24" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5459,6 +5567,11 @@
     <row r="25" ht="130.2" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -5478,47 +5591,47 @@
           </r>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>~1,000-2,000 (aggregator est.)</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Life insurance &amp; asset management</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>Mumbai, Pune</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="J25" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr">
+      <c r="K25" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5605,7 +5718,7 @@
           </r>
         </is>
       </c>
-      <c r="K25" s="15" t="inlineStr">
+      <c r="L25" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5684,7 +5797,7 @@
           </r>
         </is>
       </c>
-      <c r="L25" s="15" t="inlineStr">
+      <c r="M25" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5759,6 +5872,11 @@
     <row r="26" ht="130.2" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -5778,47 +5896,47 @@
           </r>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>~2,300-2,500 (+~220 Chennai)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>P&amp;C insurance</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Hyderabad, Bengaluru, Bhubaneswar, Chennai (2026, announced)</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" s="18" t="inlineStr">
+      <c r="J26" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="K26" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5889,7 +6007,7 @@
           </r>
         </is>
       </c>
-      <c r="K26" s="19" t="inlineStr">
+      <c r="L26" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5951,7 +6069,7 @@
           </r>
         </is>
       </c>
-      <c r="L26" s="19" t="inlineStr">
+      <c r="M26" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6026,6 +6144,11 @@
     <row r="27" ht="109.5" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -6045,47 +6168,47 @@
           </r>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>~2,000</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Life, group benefits &amp; retirement</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Sold to HCLTech (Jul 2026)</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>Chennai, Gurugram</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I27" s="14" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
+      <c r="K27" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6140,7 +6263,7 @@
           </r>
         </is>
       </c>
-      <c r="K27" s="15" t="inlineStr">
+      <c r="L27" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6183,7 +6306,7 @@
           </r>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr">
+      <c r="M27" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6258,6 +6381,11 @@
     <row r="28" ht="171.6" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -6277,47 +6405,47 @@
           </r>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>~3,500</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Retirement &amp; annuities</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Mumbai, Pune (new campus Dec 2026)</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="K28" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6404,7 +6532,7 @@
           </r>
         </is>
       </c>
-      <c r="K28" s="19" t="inlineStr">
+      <c r="L28" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6485,7 +6613,7 @@
           </r>
         </is>
       </c>
-      <c r="L28" s="19" t="inlineStr">
+      <c r="M28" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6560,6 +6688,11 @@
     <row r="29" ht="161.25" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -6579,47 +6712,47 @@
           </r>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>~3,030 (GPTW)</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Life &amp; health insurance, asset management</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>Gurugram, Bengaluru</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G29" s="14" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I29" s="14" t="inlineStr">
+      <c r="J29" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J29" s="15" t="inlineStr">
+      <c r="K29" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6690,7 +6823,7 @@
           </r>
         </is>
       </c>
-      <c r="K29" s="15" t="inlineStr">
+      <c r="L29" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6753,7 +6886,7 @@
           </r>
         </is>
       </c>
-      <c r="L29" s="15" t="inlineStr">
+      <c r="M29" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6828,6 +6961,11 @@
     <row r="30" ht="99.14999999999999" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -6847,47 +6985,47 @@
           </r>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>30,000+ (3rd party ~40,000; target 45,000 by 2027)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Health insurance / health services</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Gurugram, Hyderabad, Bengaluru, Chennai (2025), Noida</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H30" s="18" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I30" s="18" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="K30" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6942,7 +7080,7 @@
           </r>
         </is>
       </c>
-      <c r="K30" s="19" t="inlineStr">
+      <c r="L30" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6985,7 +7123,7 @@
           </r>
         </is>
       </c>
-      <c r="L30" s="19" t="inlineStr">
+      <c r="M30" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7060,6 +7198,11 @@
     <row r="31" ht="150.9" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -7079,47 +7222,47 @@
           </r>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Not disclosed (target 400+ by 2028)</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Life &amp; health insurance (Asia, Africa)</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>Bengaluru (2025)</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I31" s="14" t="inlineStr">
+      <c r="J31" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J31" s="15" t="inlineStr">
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7190,7 +7333,7 @@
           </r>
         </is>
       </c>
-      <c r="K31" s="15" t="inlineStr">
+      <c r="L31" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7252,7 +7395,7 @@
           </r>
         </is>
       </c>
-      <c r="L31" s="15" t="inlineStr">
+      <c r="M31" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7327,6 +7470,11 @@
     <row r="32" ht="86.5" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -7346,47 +7494,47 @@
           </r>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>Not disclosed (~4,000 indicative)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Retirement, insurance &amp; asset management</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>Pune, Hyderabad</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G32" s="18" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="J32" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7457,7 +7605,7 @@
           </r>
         </is>
       </c>
-      <c r="K32" s="19" t="inlineStr">
+      <c r="L32" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7518,7 +7666,7 @@
           </r>
         </is>
       </c>
-      <c r="L32" s="19" t="inlineStr">
+      <c r="M32" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7593,6 +7741,11 @@
     <row r="33" ht="78.45" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -7612,47 +7765,47 @@
           </r>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Multinational commercial P&amp;C insurance</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>Pune (2025)</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="G33" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I33" s="14" t="inlineStr">
+      <c r="J33" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J33" s="15" t="inlineStr">
+      <c r="K33" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7707,7 +7860,7 @@
           </r>
         </is>
       </c>
-      <c r="K33" s="15" t="inlineStr">
+      <c r="L33" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7749,7 +7902,7 @@
           </r>
         </is>
       </c>
-      <c r="L33" s="15" t="inlineStr">
+      <c r="M33" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7824,6 +7977,11 @@
     <row r="34" ht="57.75" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -7843,47 +8001,47 @@
           </r>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>~557 (GPTW)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>P&amp;C, life &amp; health insurance</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H34" s="18" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="18" t="inlineStr">
+      <c r="J34" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="K34" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7922,7 +8080,7 @@
           </r>
         </is>
       </c>
-      <c r="K34" s="19" t="inlineStr">
+      <c r="L34" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7945,7 +8103,7 @@
           </r>
         </is>
       </c>
-      <c r="L34" s="19" t="inlineStr">
+      <c r="M34" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8020,6 +8178,11 @@
     <row r="35" ht="57.75" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -8039,47 +8202,47 @@
           </r>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Not disclosed (target ~1,200)</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>P&amp;C and group benefits insurance</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Assisted build (Capgemini)</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="F35" s="13" t="inlineStr">
         <is>
           <t>Hyderabad (2025)</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="I35" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="J35" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J35" s="15" t="inlineStr">
+      <c r="K35" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8118,7 +8281,7 @@
           </r>
         </is>
       </c>
-      <c r="K35" s="15" t="inlineStr">
+      <c r="L35" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8141,7 +8304,7 @@
           </r>
         </is>
       </c>
-      <c r="L35" s="15" t="inlineStr">
+      <c r="M35" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8216,6 +8379,11 @@
     <row r="36" ht="119.85" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -8235,47 +8403,47 @@
           </r>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Not disclosed (1,000+ roles planned)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>P&amp;C and life insurance</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>Hyderabad (2026)</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr">
+      <c r="J36" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="K36" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8346,7 +8514,7 @@
           </r>
         </is>
       </c>
-      <c r="K36" s="19" t="inlineStr">
+      <c r="L36" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8407,7 +8575,7 @@
           </r>
         </is>
       </c>
-      <c r="L36" s="19" t="inlineStr">
+      <c r="M36" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8482,6 +8650,11 @@
     <row r="37" ht="78.45" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -8501,47 +8674,47 @@
           </r>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>18,000+</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Health insurance / health services</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>Bengaluru, Hyderabad, Gurugram</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="J37" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J37" s="15" t="inlineStr">
+      <c r="K37" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8596,7 +8769,7 @@
           </r>
         </is>
       </c>
-      <c r="K37" s="15" t="inlineStr">
+      <c r="L37" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8638,7 +8811,7 @@
           </r>
         </is>
       </c>
-      <c r="L37" s="15" t="inlineStr">
+      <c r="M37" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8713,6 +8886,11 @@
     <row r="38" ht="98" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -8732,47 +8910,47 @@
           </r>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>P&amp;C insurance</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="E38" s="17" t="inlineStr">
         <is>
           <t>Captive via acquisition (RSA)</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="F38" s="17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H38" s="18" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J38" s="19" t="inlineStr">
+      <c r="K38" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8843,7 +9021,7 @@
           </r>
         </is>
       </c>
-      <c r="K38" s="19" t="inlineStr">
+      <c r="L38" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8904,7 +9082,7 @@
           </r>
         </is>
       </c>
-      <c r="L38" s="19" t="inlineStr">
+      <c r="M38" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8979,6 +9157,11 @@
     <row r="39" ht="54.3" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -8998,47 +9181,47 @@
           </r>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Life insurance, retirement &amp; asset management</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>Gurugram (2026)</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J39" s="15" t="inlineStr">
+      <c r="K39" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9077,7 +9260,7 @@
           </r>
         </is>
       </c>
-      <c r="K39" s="15" t="inlineStr">
+      <c r="L39" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9100,7 +9283,7 @@
           </r>
         </is>
       </c>
-      <c r="L39" s="15" t="inlineStr">
+      <c r="M39" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9175,6 +9358,11 @@
     <row r="40" ht="109.5" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -9194,47 +9382,47 @@
           </r>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>~537 (GPTW)</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="D40" s="17" t="inlineStr">
         <is>
           <t>Device, auto &amp; home protection insurance</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="E40" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="F40" s="17" t="inlineStr">
         <is>
           <t>Chennai, Bengaluru, Mumbai, Hyderabad, Gurugram</t>
         </is>
       </c>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="J40" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J40" s="19" t="inlineStr">
+      <c r="K40" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9305,7 +9493,7 @@
           </r>
         </is>
       </c>
-      <c r="K40" s="19" t="inlineStr">
+      <c r="L40" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9367,7 +9555,7 @@
           </r>
         </is>
       </c>
-      <c r="L40" s="19" t="inlineStr">
+      <c r="M40" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9442,6 +9630,11 @@
     <row r="41" ht="57.75" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -9461,47 +9654,47 @@
           </r>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>~60 at launch (Jul 2026; target 100+)</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>P&amp;C insurance &amp; financial services</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>Hyderabad (2026)</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="K41" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9540,7 +9733,7 @@
           </r>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
+      <c r="L41" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9563,7 +9756,7 @@
           </r>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr">
+      <c r="M41" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9638,6 +9831,11 @@
     <row r="42" ht="54.3" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -9657,47 +9855,47 @@
           </r>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Long-term care insurance</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G42" s="18" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H42" s="18" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="18" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J42" s="19" t="inlineStr">
+      <c r="K42" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9736,7 +9934,7 @@
           </r>
         </is>
       </c>
-      <c r="K42" s="19" t="inlineStr">
+      <c r="L42" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9758,7 +9956,7 @@
           </r>
         </is>
       </c>
-      <c r="L42" s="19" t="inlineStr">
+      <c r="M42" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9833,6 +10031,11 @@
     <row r="43" ht="192.3" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -9852,47 +10055,47 @@
           </r>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>~3,000+ (Jun 2026)</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>Retirement, benefits &amp; investment management</t>
         </is>
       </c>
-      <c r="D43" s="12" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Captive via acquisition (SLK Software JV stake, 2023)</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>Bengaluru, Hyderabad (2026)</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I43" s="14" t="inlineStr">
+      <c r="J43" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J43" s="15" t="inlineStr">
+      <c r="K43" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9969,7 +10172,7 @@
           </r>
         </is>
       </c>
-      <c r="K43" s="15" t="inlineStr">
+      <c r="L43" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10051,7 +10254,7 @@
           </r>
         </is>
       </c>
-      <c r="L43" s="15" t="inlineStr">
+      <c r="M43" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10126,6 +10329,11 @@
     <row r="44" ht="75" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -10145,47 +10353,47 @@
           </r>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>~4,000</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="D44" s="17" t="inlineStr">
         <is>
           <t>Title insurance</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F44" s="18" t="inlineStr">
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G44" s="18" t="inlineStr">
+      <c r="H44" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H44" s="18" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I44" s="18" t="inlineStr">
+      <c r="J44" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J44" s="19" t="inlineStr">
+      <c r="K44" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10240,7 +10448,7 @@
           </r>
         </is>
       </c>
-      <c r="K44" s="19" t="inlineStr">
+      <c r="L44" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10282,7 +10490,7 @@
           </r>
         </is>
       </c>
-      <c r="L44" s="19" t="inlineStr">
+      <c r="M44" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10370,11 +10578,17 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
-      <c r="L45" s="11" t="n"/>
+      <c r="L45" s="10" t="n"/>
+      <c r="M45" s="11" t="n"/>
     </row>
     <row r="46" ht="78.45" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -10394,47 +10608,47 @@
           </r>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>~15 (FY26 NL-41 filing; 4 in Sep 2024)</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D46" s="12" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="F46" s="13" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="K46" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10489,7 +10703,7 @@
           </r>
         </is>
       </c>
-      <c r="K46" s="15" t="inlineStr">
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10531,7 +10745,7 @@
           </r>
         </is>
       </c>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="M46" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10606,6 +10820,11 @@
     <row r="47" ht="98" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -10625,47 +10844,47 @@
           </r>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>~705 (Revelio Labs, Dec 2025)</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Retirement recordkeeping (Empower)</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F47" s="18" t="inlineStr">
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G47" s="18" t="inlineStr">
+      <c r="H47" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H47" s="18" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I47" s="18" t="inlineStr">
+      <c r="J47" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="K47" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10736,7 +10955,7 @@
           </r>
         </is>
       </c>
-      <c r="K47" s="19" t="inlineStr">
+      <c r="L47" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10797,7 +11016,7 @@
           </r>
         </is>
       </c>
-      <c r="L47" s="19" t="inlineStr">
+      <c r="M47" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10872,6 +11091,11 @@
     <row r="48" ht="57.75" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -10891,47 +11115,47 @@
           </r>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="K48" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10970,7 +11194,7 @@
           </r>
         </is>
       </c>
-      <c r="K48" s="15" t="inlineStr">
+      <c r="L48" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10993,7 +11217,7 @@
           </r>
         </is>
       </c>
-      <c r="L48" s="15" t="inlineStr">
+      <c r="M48" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11068,6 +11292,11 @@
     <row r="49" ht="54.3" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -11087,47 +11316,47 @@
           </r>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Reinsurance platform (IRDAI branch &amp; GIFT City)</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI); IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>Mumbai, GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F49" s="18" t="inlineStr">
+      <c r="G49" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G49" s="18" t="inlineStr">
+      <c r="H49" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="18" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I49" s="18" t="inlineStr">
+      <c r="J49" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J49" s="19" t="inlineStr">
+      <c r="K49" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11166,7 +11395,7 @@
           </r>
         </is>
       </c>
-      <c r="K49" s="19" t="inlineStr">
+      <c r="L49" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11189,7 +11418,7 @@
           </r>
         </is>
       </c>
-      <c r="L49" s="19" t="inlineStr">
+      <c r="M49" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11264,6 +11493,11 @@
     <row r="50" ht="57.75" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -11283,47 +11517,47 @@
           </r>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>~144 (FY25 NL-41 filing, not re-verified)</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="G50" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="I50" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J50" s="15" t="inlineStr">
+      <c r="K50" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11362,7 +11596,7 @@
           </r>
         </is>
       </c>
-      <c r="K50" s="15" t="inlineStr">
+      <c r="L50" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11385,7 +11619,7 @@
           </r>
         </is>
       </c>
-      <c r="L50" s="15" t="inlineStr">
+      <c r="M50" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11460,6 +11694,11 @@
     <row r="51" ht="54.3" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -11479,47 +11718,47 @@
           </r>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>Life &amp; health reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="F51" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F51" s="18" t="inlineStr">
+      <c r="G51" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G51" s="18" t="inlineStr">
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I51" s="18" t="inlineStr">
+      <c r="J51" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J51" s="19" t="inlineStr">
+      <c r="K51" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11558,7 +11797,7 @@
           </r>
         </is>
       </c>
-      <c r="K51" s="19" t="inlineStr">
+      <c r="L51" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11581,7 +11820,7 @@
           </r>
         </is>
       </c>
-      <c r="L51" s="19" t="inlineStr">
+      <c r="M51" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11656,6 +11895,11 @@
     <row r="52" ht="99.14999999999999" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -11675,47 +11919,47 @@
           </r>
         </is>
       </c>
-      <c r="B52" s="13" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>~30 (2022)</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F52" s="14" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="H52" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr">
+      <c r="I52" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I52" s="14" t="inlineStr">
+      <c r="J52" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J52" s="15" t="inlineStr">
+      <c r="K52" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11770,7 +12014,7 @@
           </r>
         </is>
       </c>
-      <c r="K52" s="15" t="inlineStr">
+      <c r="L52" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11812,7 +12056,7 @@
           </r>
         </is>
       </c>
-      <c r="L52" s="15" t="inlineStr">
+      <c r="M52" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11887,6 +12131,11 @@
     <row r="53" ht="109.5" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -11906,47 +12155,47 @@
           </r>
         </is>
       </c>
-      <c r="B53" s="17" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>~2,000+ (company); ~2,374 (Tracxn, 2025)</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GCC + IRDAI branch)</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>Captive (self-built); Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="F53" s="17" t="inlineStr">
         <is>
           <t>Bengaluru, Hyderabad (2022), Mumbai (branch)</t>
         </is>
       </c>
-      <c r="F53" s="18" t="inlineStr">
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G53" s="18" t="inlineStr">
+      <c r="H53" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I53" s="18" t="inlineStr">
+      <c r="J53" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="K53" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12017,7 +12266,7 @@
           </r>
         </is>
       </c>
-      <c r="K53" s="19" t="inlineStr">
+      <c r="L53" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12078,7 +12327,7 @@
           </r>
         </is>
       </c>
-      <c r="L53" s="19" t="inlineStr">
+      <c r="M53" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12153,6 +12402,11 @@
     <row r="54" ht="54.3" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -12172,47 +12426,47 @@
           </r>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>None (never operational)</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
         <is>
           <t>Lloyd's syndicate service company</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>Withdrawn (Mar 2026)</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="F54" s="13" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="14" t="inlineStr">
+      <c r="H54" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr">
+      <c r="I54" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="14" t="inlineStr">
+      <c r="J54" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J54" s="15" t="inlineStr">
+      <c r="K54" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12235,8 +12489,8 @@
           </r>
         </is>
       </c>
-      <c r="K54" s="15" t="inlineStr"/>
-      <c r="L54" s="15" t="inlineStr">
+      <c r="L54" s="15" t="inlineStr"/>
+      <c r="M54" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12311,6 +12565,11 @@
     <row r="55" ht="75" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -12330,47 +12589,47 @@
           </r>
         </is>
       </c>
-      <c r="B55" s="17" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>~15 (FY26 NL-41 filing; 4 in Sep 2024)</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI branch)</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>Regulated branch (IRDAI)</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F55" s="18" t="inlineStr">
+      <c r="G55" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G55" s="18" t="inlineStr">
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I55" s="18" t="inlineStr">
+      <c r="J55" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J55" s="19" t="inlineStr">
+      <c r="K55" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12425,7 +12684,7 @@
           </r>
         </is>
       </c>
-      <c r="K55" s="19" t="inlineStr">
+      <c r="L55" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12467,7 +12726,7 @@
           </r>
         </is>
       </c>
-      <c r="L55" s="19" t="inlineStr">
+      <c r="M55" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12542,6 +12801,11 @@
     <row r="56" ht="119.85" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -12561,47 +12825,47 @@
           </r>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>~4,000+ (2023); ~4,570 (Mar 2026, GDC entity only)</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="D56" s="13" t="inlineStr">
         <is>
           <t>Insurance broking &amp; advisory GDC</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>Captive (self-built)</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="F56" s="13" t="inlineStr">
         <is>
           <t>Mumbai, Gurugram, Kolkata, Siliguri</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
+      <c r="H56" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H56" s="14" t="inlineStr">
+      <c r="I56" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I56" s="14" t="inlineStr">
+      <c r="J56" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J56" s="15" t="inlineStr">
+      <c r="K56" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12672,7 +12936,7 @@
           </r>
         </is>
       </c>
-      <c r="K56" s="15" t="inlineStr">
+      <c r="L56" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12733,7 +12997,7 @@
           </r>
         </is>
       </c>
-      <c r="L56" s="15" t="inlineStr">
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12808,6 +13072,11 @@
     <row r="57" ht="68.09999999999999" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -12827,47 +13096,47 @@
           </r>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>~241 broking associates (target ~380); services entity ~8</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Insurance &amp; reinsurance broking</t>
         </is>
       </c>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="E57" s="17" t="inlineStr">
         <is>
           <t>Broking entity (IRDAI) via acquisition of Arihant (2024)</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="F57" s="17" t="inlineStr">
         <is>
           <t>Mumbai, Delhi, Kolkata, Bengaluru, Chennai</t>
         </is>
       </c>
-      <c r="F57" s="18" t="inlineStr">
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="18" t="inlineStr">
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I57" s="18" t="inlineStr">
+      <c r="J57" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J57" s="19" t="inlineStr">
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12906,7 +13175,7 @@
           </r>
         </is>
       </c>
-      <c r="K57" s="19" t="inlineStr">
+      <c r="L57" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12929,7 +13198,7 @@
           </r>
         </is>
       </c>
-      <c r="L57" s="19" t="inlineStr">
+      <c r="M57" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13004,6 +13273,11 @@
     <row r="58" ht="99.14999999999999" customHeight="1">
       <c r="A58" s="12" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -13014,47 +13288,47 @@
           </r>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>Specialty insurance &amp; reinsurance broker</t>
         </is>
       </c>
-      <c r="D58" s="12" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>Assisted build (EY advised)</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="F58" s="13" t="inlineStr">
         <is>
           <t>Mumbai (2026)</t>
         </is>
       </c>
-      <c r="F58" s="14" t="inlineStr">
+      <c r="G58" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G58" s="14" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H58" s="14" t="inlineStr">
+      <c r="I58" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I58" s="14" t="inlineStr">
+      <c r="J58" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J58" s="15" t="inlineStr">
+      <c r="K58" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13109,7 +13383,7 @@
           </r>
         </is>
       </c>
-      <c r="K58" s="15" t="inlineStr">
+      <c r="L58" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13152,7 +13426,7 @@
           </r>
         </is>
       </c>
-      <c r="L58" s="15" t="inlineStr">
+      <c r="M58" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13240,11 +13514,17 @@
       <c r="I59" s="10" t="n"/>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="10" t="n"/>
-      <c r="L59" s="11" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="11" t="n"/>
     </row>
     <row r="60" ht="57.75" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -13264,47 +13544,47 @@
           </r>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C60" s="16" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (IRDAI domestic reinsurer)</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="E60" s="17" t="inlineStr">
         <is>
           <t>JV (Allianz Europe / Jio Financial Services)</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="F60" s="17" t="inlineStr">
         <is>
           <t>Mumbai (2026)</t>
         </is>
       </c>
-      <c r="F60" s="18" t="inlineStr">
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="18" t="inlineStr">
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
+      <c r="J60" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="K60" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13343,7 +13623,7 @@
           </r>
         </is>
       </c>
-      <c r="K60" s="19" t="inlineStr">
+      <c r="L60" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13366,7 +13646,7 @@
           </r>
         </is>
       </c>
-      <c r="L60" s="19" t="inlineStr">
+      <c r="M60" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13441,6 +13721,11 @@
     <row r="61" ht="54.3" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -13460,47 +13745,47 @@
           </r>
         </is>
       </c>
-      <c r="B61" s="13" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="F61" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F61" s="14" t="inlineStr">
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G61" s="14" t="inlineStr">
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H61" s="14" t="inlineStr">
+      <c r="I61" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I61" s="14" t="inlineStr">
+      <c r="J61" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J61" s="15" t="inlineStr">
+      <c r="K61" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13539,7 +13824,7 @@
           </r>
         </is>
       </c>
-      <c r="K61" s="15" t="inlineStr">
+      <c r="L61" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13562,7 +13847,7 @@
           </r>
         </is>
       </c>
-      <c r="L61" s="15" t="inlineStr">
+      <c r="M61" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13637,6 +13922,11 @@
     <row r="62" ht="88.8" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -13656,47 +13946,47 @@
           </r>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C62" s="16" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="E62" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="F62" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F62" s="18" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G62" s="18" t="inlineStr">
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I62" s="18" t="inlineStr">
+      <c r="J62" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J62" s="19" t="inlineStr">
+      <c r="K62" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13751,7 +14041,7 @@
           </r>
         </is>
       </c>
-      <c r="K62" s="19" t="inlineStr">
+      <c r="L62" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13793,7 +14083,7 @@
           </r>
         </is>
       </c>
-      <c r="L62" s="19" t="inlineStr">
+      <c r="M62" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13868,6 +14158,11 @@
     <row r="63" ht="68.09999999999999" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -13887,47 +14182,47 @@
           </r>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="F63" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2025)</t>
         </is>
       </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G63" s="14" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H63" s="14" t="inlineStr">
+      <c r="I63" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I63" s="14" t="inlineStr">
+      <c r="J63" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J63" s="15" t="inlineStr">
+      <c r="K63" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13966,7 +14261,7 @@
           </r>
         </is>
       </c>
-      <c r="K63" s="15" t="inlineStr">
+      <c r="L63" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13989,7 +14284,7 @@
           </r>
         </is>
       </c>
-      <c r="L63" s="15" t="inlineStr">
+      <c r="M63" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14064,6 +14359,11 @@
     <row r="64" ht="99.14999999999999" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -14083,47 +14383,47 @@
           </r>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Specialty insurance &amp; reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="E64" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="F64" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2025)</t>
         </is>
       </c>
-      <c r="F64" s="18" t="inlineStr">
+      <c r="G64" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="18" t="inlineStr">
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H64" s="18" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="J64" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14178,7 +14478,7 @@
           </r>
         </is>
       </c>
-      <c r="K64" s="19" t="inlineStr">
+      <c r="L64" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14220,7 +14520,7 @@
           </r>
         </is>
       </c>
-      <c r="L64" s="19" t="inlineStr">
+      <c r="M64" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14295,6 +14595,11 @@
     <row r="65" ht="54.3" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -14314,47 +14619,47 @@
           </r>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="F65" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G65" s="14" t="inlineStr">
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H65" s="14" t="inlineStr">
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I65" s="14" t="inlineStr">
+      <c r="J65" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J65" s="15" t="inlineStr">
+      <c r="K65" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14393,7 +14698,7 @@
           </r>
         </is>
       </c>
-      <c r="K65" s="15" t="inlineStr">
+      <c r="L65" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14416,7 +14721,7 @@
           </r>
         </is>
       </c>
-      <c r="L65" s="15" t="inlineStr">
+      <c r="M65" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14491,6 +14796,11 @@
     <row r="66" ht="54.3" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -14510,47 +14820,47 @@
           </r>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="C66" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="F66" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F66" s="18" t="inlineStr">
+      <c r="G66" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G66" s="18" t="inlineStr">
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="J66" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="K66" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14589,7 +14899,7 @@
           </r>
         </is>
       </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="L66" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14612,7 +14922,7 @@
           </r>
         </is>
       </c>
-      <c r="L66" s="19" t="inlineStr">
+      <c r="M66" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14687,6 +14997,11 @@
     <row r="67" ht="57.75" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -14706,47 +15021,47 @@
           </r>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="F67" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F67" s="14" t="inlineStr">
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G67" s="14" t="inlineStr">
+      <c r="H67" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr">
+      <c r="I67" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I67" s="14" t="inlineStr">
+      <c r="J67" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J67" s="15" t="inlineStr">
+      <c r="K67" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14785,7 +15100,7 @@
           </r>
         </is>
       </c>
-      <c r="K67" s="15" t="inlineStr">
+      <c r="L67" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14808,7 +15123,7 @@
           </r>
         </is>
       </c>
-      <c r="L67" s="15" t="inlineStr">
+      <c r="M67" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14883,6 +15198,11 @@
     <row r="68" ht="54.3" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -14902,47 +15222,47 @@
           </r>
         </is>
       </c>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="C68" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C68" s="16" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="E68" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="F68" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F68" s="18" t="inlineStr">
+      <c r="G68" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G68" s="18" t="inlineStr">
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H68" s="18" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I68" s="18" t="inlineStr">
+      <c r="J68" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J68" s="19" t="inlineStr">
+      <c r="K68" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14971,7 +15291,7 @@
           </r>
         </is>
       </c>
-      <c r="K68" s="19" t="inlineStr">
+      <c r="L68" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14994,7 +15314,7 @@
           </r>
         </is>
       </c>
-      <c r="L68" s="19" t="inlineStr">
+      <c r="M68" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15069,6 +15389,11 @@
     <row r="69" ht="57.75" customHeight="1">
       <c r="A69" s="12" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -15088,47 +15413,47 @@
           </r>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="F69" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G69" s="14" t="inlineStr">
+      <c r="H69" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H69" s="14" t="inlineStr">
+      <c r="I69" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I69" s="14" t="inlineStr">
+      <c r="J69" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J69" s="15" t="inlineStr">
+      <c r="K69" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15167,7 +15492,7 @@
           </r>
         </is>
       </c>
-      <c r="K69" s="15" t="inlineStr">
+      <c r="L69" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15190,7 +15515,7 @@
           </r>
         </is>
       </c>
-      <c r="L69" s="15" t="inlineStr">
+      <c r="M69" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15265,6 +15590,11 @@
     <row r="70" ht="57.75" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -15284,47 +15614,47 @@
           </r>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C70" s="16" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="E70" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="F70" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F70" s="18" t="inlineStr">
+      <c r="G70" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G70" s="18" t="inlineStr">
+      <c r="H70" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H70" s="18" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I70" s="18" t="inlineStr">
+      <c r="J70" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J70" s="19" t="inlineStr">
+      <c r="K70" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15363,7 +15693,7 @@
           </r>
         </is>
       </c>
-      <c r="K70" s="19" t="inlineStr">
+      <c r="L70" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15386,7 +15716,7 @@
           </r>
         </is>
       </c>
-      <c r="L70" s="19" t="inlineStr">
+      <c r="M70" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15461,6 +15791,11 @@
     <row r="71" ht="54.3" customHeight="1">
       <c r="A71" s="12" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -15480,47 +15815,47 @@
           </r>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="F71" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F71" s="14" t="inlineStr">
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="14" t="inlineStr">
+      <c r="H71" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H71" s="14" t="inlineStr">
+      <c r="I71" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I71" s="14" t="inlineStr">
+      <c r="J71" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J71" s="15" t="inlineStr">
+      <c r="K71" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15559,7 +15894,7 @@
           </r>
         </is>
       </c>
-      <c r="K71" s="15" t="inlineStr">
+      <c r="L71" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15582,7 +15917,7 @@
           </r>
         </is>
       </c>
-      <c r="L71" s="15" t="inlineStr">
+      <c r="M71" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15657,6 +15992,11 @@
     <row r="72" ht="88.8" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -15676,47 +16016,47 @@
           </r>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F72" s="18" t="inlineStr">
+      <c r="G72" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G72" s="18" t="inlineStr">
+      <c r="H72" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="H72" s="18" t="inlineStr">
+      <c r="I72" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I72" s="18" t="inlineStr">
+      <c r="J72" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J72" s="19" t="inlineStr">
+      <c r="K72" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15771,7 +16111,7 @@
           </r>
         </is>
       </c>
-      <c r="K72" s="19" t="inlineStr">
+      <c r="L72" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15813,7 +16153,7 @@
           </r>
         </is>
       </c>
-      <c r="L72" s="19" t="inlineStr">
+      <c r="M72" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15888,6 +16228,11 @@
     <row r="73" ht="109.5" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -15907,47 +16252,47 @@
           </r>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>Technology-led NatCat &amp; specialty reinsurance</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2026)</t>
         </is>
       </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G73" s="14" t="inlineStr">
+      <c r="H73" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H73" s="14" t="inlineStr">
+      <c r="I73" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I73" s="14" t="inlineStr">
+      <c r="J73" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J73" s="15" t="inlineStr">
+      <c r="K73" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16002,7 +16347,7 @@
           </r>
         </is>
       </c>
-      <c r="K73" s="15" t="inlineStr">
+      <c r="L73" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16045,7 +16390,7 @@
           </r>
         </is>
       </c>
-      <c r="L73" s="15" t="inlineStr">
+      <c r="M73" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16120,6 +16465,11 @@
     <row r="74" ht="68.09999999999999" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -16139,47 +16489,47 @@
           </r>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2024)</t>
         </is>
       </c>
-      <c r="F74" s="18" t="inlineStr">
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G74" s="18" t="inlineStr">
+      <c r="H74" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I74" s="18" t="inlineStr">
+      <c r="J74" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J74" s="19" t="inlineStr">
+      <c r="K74" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16218,7 +16568,7 @@
           </r>
         </is>
       </c>
-      <c r="K74" s="19" t="inlineStr">
+      <c r="L74" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16241,7 +16591,7 @@
           </r>
         </is>
       </c>
-      <c r="L74" s="19" t="inlineStr">
+      <c r="M74" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16316,6 +16666,11 @@
     <row r="75" ht="57.75" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -16335,47 +16690,47 @@
           </r>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="F75" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2025)</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="G75" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G75" s="14" t="inlineStr">
+      <c r="H75" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H75" s="14" t="inlineStr">
+      <c r="I75" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I75" s="14" t="inlineStr">
+      <c r="J75" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J75" s="15" t="inlineStr">
+      <c r="K75" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16414,7 +16769,7 @@
           </r>
         </is>
       </c>
-      <c r="K75" s="15" t="inlineStr">
+      <c r="L75" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16437,7 +16792,7 @@
           </r>
         </is>
       </c>
-      <c r="L75" s="15" t="inlineStr">
+      <c r="M75" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16512,6 +16867,11 @@
     <row r="76" ht="57.75" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -16531,47 +16891,47 @@
           </r>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C76" s="16" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="F76" s="17" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2025)</t>
         </is>
       </c>
-      <c r="F76" s="18" t="inlineStr">
+      <c r="G76" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G76" s="18" t="inlineStr">
+      <c r="H76" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="I76" s="18" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I76" s="18" t="inlineStr">
+      <c r="J76" s="18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J76" s="19" t="inlineStr">
+      <c r="K76" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16600,7 +16960,7 @@
           </r>
         </is>
       </c>
-      <c r="K76" s="19" t="inlineStr">
+      <c r="L76" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16623,7 +16983,7 @@
           </r>
         </is>
       </c>
-      <c r="L76" s="19" t="inlineStr">
+      <c r="M76" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16698,6 +17058,11 @@
     <row r="77" ht="57.75" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Arial"/>
@@ -16717,47 +17082,47 @@
           </r>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>Not disclosed</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>Reinsurance (GIFT City IFSC office)</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>IFSC Insurance Office (IFSCA, GIFT City)</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="F77" s="13" t="inlineStr">
         <is>
           <t>GIFT City, Gandhinagar (2025)</t>
         </is>
       </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="G77" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G77" s="14" t="inlineStr">
+      <c r="H77" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H77" s="14" t="inlineStr">
+      <c r="I77" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I77" s="14" t="inlineStr">
+      <c r="J77" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J77" s="15" t="inlineStr">
+      <c r="K77" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16796,7 +17161,7 @@
           </r>
         </is>
       </c>
-      <c r="K77" s="15" t="inlineStr">
+      <c r="L77" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16819,7 +17184,7 @@
           </r>
         </is>
       </c>
-      <c r="L77" s="15" t="inlineStr">
+      <c r="M77" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16899,18 +17264,19 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A59:L59"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="F2:L2"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A79:M79"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A4:M4"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A79:L79"/>
-    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="G2:M2"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
